--- a/artifacts/exports/shuori-demo-monthly-report.xlsx
+++ b/artifacts/exports/shuori-demo-monthly-report.xlsx
@@ -13,9 +13,10 @@
     <sheet sheetId="7" name="Activity records" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Shifts" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Assignment roster" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Field dictionary" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A1:$C13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A1:$C14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Overview'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Monthly summary'!$A1:$C16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Monthly summary'!$1:$5</definedName>
@@ -27,24 +28,26 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Service categories'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Six month trend'!$A1:$B11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Six month trend'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Activity records'!$A1:$M46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Activity records'!$A1:$O46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Activity records'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Shifts'!$A1:$T41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Shifts'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Assignment roster'!$A1:$N50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Assignment roster'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Field dictionary'!$A1:$L5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Field dictionary'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="236">
   <si>
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 10:10:32 JST · Asia/Tokyo · demo · version 1.2.0</t>
+    <t>Generated 2026-10-08 17:07:00 JST · Asia/Tokyo · demo · version 1.3.0</t>
   </si>
   <si>
     <t>monthly-report | All records in the stated scope | Month: 2026-10 | View label: 2026-10 | activity and participation</t>
@@ -104,6 +107,12 @@
     <t>One row per volunteer/shift assignment. Historical completed or cancelled shifts are preserved without applying current readiness retroactively.</t>
   </si>
   <si>
+    <t>Field dictionary</t>
+  </si>
+  <si>
+    <t>Custom columns retain stable field IDs, labels and native value types. Archived definitions and existing values remain exportable. An empty selected scope includes headers only.</t>
+  </si>
+  <si>
     <t>守織 SHUORI · Monthly summary</t>
   </si>
   <si>
@@ -323,6 +332,12 @@
     <t>Shift</t>
   </si>
   <si>
+    <t>Event ID</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -705,6 +720,36 @@
   </si>
   <si>
     <t>Eligible</t>
+  </si>
+  <si>
+    <t>守織 SHUORI · Field dictionary</t>
+  </si>
+  <si>
+    <t>No matching records. Column headers are retained. Custom columns retain stable field IDs, labels and native value types. Archived definitions and existing values remain exportable. An empty selected scope includes headers only.</t>
+  </si>
+  <si>
+    <t>Applies to</t>
+  </si>
+  <si>
+    <t>Field label</t>
+  </si>
+  <si>
+    <t>Value type</t>
+  </si>
+  <si>
+    <t>Select options</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Display order</t>
+  </si>
+  <si>
+    <t>Definition status</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1240,7 @@
     <tabColor rgb="FF00A7CB"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1330,13 +1375,164 @@
         <v>20</v>
       </c>
     </row>
+    <row r="14" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:C13"/>
+  <autoFilter ref="A5:C14"/>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L守織 SHUORI&amp;CVolunteer operations&amp;RAsia/Tokyo</oddHeader>
+    <oddFooter>&amp;LInternal operational export&amp;C&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00A7CB"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="65" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="12" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" ht="23" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:L5"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1363,7 +1559,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1384,97 +1580,97 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="9">
         <v>102</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="8">
         <v>673</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" s="9">
         <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="8">
         <v>8.5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="9">
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="8">
         <v>36</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1485,40 +1681,40 @@
         <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="8">
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="9">
         <v>62</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B16" s="8">
         <v>64.51612903225806</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1752,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1596,30 +1792,30 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5">
         <v>5</v>
@@ -1636,10 +1832,10 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" s="7">
         <v>5</v>
@@ -1656,10 +1852,10 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5">
         <v>5</v>
@@ -1676,10 +1872,10 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="7">
         <v>4</v>
@@ -1696,10 +1892,10 @@
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
@@ -1716,10 +1912,10 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7">
         <v>4</v>
@@ -1736,10 +1932,10 @@
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" s="5">
         <v>3</v>
@@ -1756,10 +1952,10 @@
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" s="7">
         <v>3</v>
@@ -1776,10 +1972,10 @@
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" s="5">
         <v>3</v>
@@ -1796,10 +1992,10 @@
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" s="7">
         <v>2</v>
@@ -1816,10 +2012,10 @@
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" s="5">
         <v>2</v>
@@ -1836,10 +2032,10 @@
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -1889,7 +2085,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1929,30 +2125,30 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5">
         <v>5</v>
@@ -1969,10 +2165,10 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" s="7">
         <v>5</v>
@@ -1989,10 +2185,10 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5">
         <v>5</v>
@@ -2009,10 +2205,10 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="7">
         <v>4</v>
@@ -2029,10 +2225,10 @@
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
@@ -2049,10 +2245,10 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7">
         <v>4</v>
@@ -2069,10 +2265,10 @@
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" s="5">
         <v>3</v>
@@ -2089,10 +2285,10 @@
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" s="7">
         <v>3</v>
@@ -2109,10 +2305,10 @@
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" s="5">
         <v>3</v>
@@ -2129,10 +2325,10 @@
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" s="7">
         <v>2</v>
@@ -2149,10 +2345,10 @@
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" s="5">
         <v>2</v>
@@ -2169,10 +2365,10 @@
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2220,7 +2416,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2241,25 +2437,25 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" s="10">
         <v>90</v>
@@ -2270,7 +2466,7 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" s="12">
         <v>12</v>
@@ -2311,7 +2507,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -2329,21 +2525,21 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="10">
         <v>0</v>
@@ -2351,7 +2547,7 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B7" s="12">
         <v>0</v>
@@ -2359,7 +2555,7 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B8" s="10">
         <v>0</v>
@@ -2367,7 +2563,7 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B9" s="12">
         <v>0</v>
@@ -2375,7 +2571,7 @@
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="10">
         <v>62</v>
@@ -2383,7 +2579,7 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="12">
         <v>102</v>
@@ -2412,25 +2608,27 @@
     <tabColor rgb="FF00A7CB"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="39" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="13" width="23" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="55" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2444,8 +2642,10 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" ht="23" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" ht="23" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2461,8 +2661,10 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2478,8 +2680,10 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -2495,1736 +2699,1826 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="14">
+        <v>105</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="14">
         <v>46296</v>
       </c>
-      <c r="G6" s="10">
+      <c r="I6" s="10">
         <v>3</v>
       </c>
-      <c r="H6" s="5">
+      <c r="J6" s="5">
         <v>19</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="5">
-        <v>1</v>
-      </c>
-      <c r="L6" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M6" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1</v>
+      </c>
+      <c r="N6" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O6" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="16">
+        <v>46296</v>
+      </c>
+      <c r="I7" s="12">
+        <v>3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>20</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O7" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="14">
+        <v>46296</v>
+      </c>
+      <c r="I8" s="10">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>21</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O8" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="16">
+        <v>46296</v>
+      </c>
+      <c r="I9" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="J9" s="7">
+        <v>19</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M9" s="7">
+        <v>1</v>
+      </c>
+      <c r="N9" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O9" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="14">
+        <v>46296</v>
+      </c>
+      <c r="I10" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>20</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" s="5">
+        <v>1</v>
+      </c>
+      <c r="N10" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O10" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="16">
+        <v>46296</v>
+      </c>
+      <c r="I11" s="12">
+        <v>2</v>
+      </c>
+      <c r="J11" s="7">
+        <v>19</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M11" s="7">
+        <v>1</v>
+      </c>
+      <c r="N11" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O11" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="14">
+        <v>46296</v>
+      </c>
+      <c r="I12" s="10">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>20</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1</v>
+      </c>
+      <c r="N12" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O12" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="16">
+        <v>46297</v>
+      </c>
+      <c r="I13" s="12">
+        <v>3</v>
+      </c>
+      <c r="J13" s="7">
+        <v>18</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M13" s="7">
+        <v>1</v>
+      </c>
+      <c r="N13" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O13" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="14">
+        <v>46297</v>
+      </c>
+      <c r="I14" s="10">
+        <v>3</v>
+      </c>
+      <c r="J14" s="5">
+        <v>19</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O14" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="16">
+        <v>46297</v>
+      </c>
+      <c r="I15" s="12">
+        <v>3</v>
+      </c>
+      <c r="J15" s="7">
+        <v>20</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15" s="7">
+        <v>1</v>
+      </c>
+      <c r="N15" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O15" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="16">
-        <v>46296</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="D16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="14">
+        <v>46297</v>
+      </c>
+      <c r="I16" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="J16" s="5">
+        <v>18</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O16" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="16">
+        <v>46297</v>
+      </c>
+      <c r="I17" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="J17" s="7">
+        <v>19</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" s="7">
+        <v>1</v>
+      </c>
+      <c r="N17" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O17" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="14">
+        <v>46297</v>
+      </c>
+      <c r="I18" s="10">
+        <v>2</v>
+      </c>
+      <c r="J18" s="5">
+        <v>18</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M18" s="5">
+        <v>1</v>
+      </c>
+      <c r="N18" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O18" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="16">
+        <v>46297</v>
+      </c>
+      <c r="I19" s="12">
+        <v>2</v>
+      </c>
+      <c r="J19" s="7">
+        <v>19</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M19" s="7">
+        <v>1</v>
+      </c>
+      <c r="N19" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O19" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="14">
+        <v>46297</v>
+      </c>
+      <c r="I20" s="10">
+        <v>2</v>
+      </c>
+      <c r="J20" s="5">
+        <v>18</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M20" s="5">
+        <v>1</v>
+      </c>
+      <c r="N20" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O20" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="16">
+        <v>46297</v>
+      </c>
+      <c r="I21" s="12">
+        <v>2</v>
+      </c>
+      <c r="J21" s="7">
+        <v>19</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M21" s="7">
+        <v>1</v>
+      </c>
+      <c r="N21" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O21" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="14">
+        <v>46300</v>
+      </c>
+      <c r="I22" s="10">
         <v>3</v>
       </c>
-      <c r="H7" s="7">
-        <v>20</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" s="7">
-        <v>1</v>
-      </c>
-      <c r="L7" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M7" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="J22" s="5">
+        <v>15</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M22" s="5">
+        <v>1</v>
+      </c>
+      <c r="N22" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O22" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="16">
+        <v>46300</v>
+      </c>
+      <c r="I23" s="12">
+        <v>3</v>
+      </c>
+      <c r="J23" s="7">
+        <v>16</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M23" s="7">
+        <v>1</v>
+      </c>
+      <c r="N23" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O23" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="14">
+        <v>46300</v>
+      </c>
+      <c r="I24" s="10">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5">
+        <v>17</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M24" s="5">
+        <v>1</v>
+      </c>
+      <c r="N24" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O24" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="16">
+        <v>46300</v>
+      </c>
+      <c r="I25" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="J25" s="7">
+        <v>15</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M25" s="7">
+        <v>1</v>
+      </c>
+      <c r="N25" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O25" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="14">
+        <v>46300</v>
+      </c>
+      <c r="I26" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="J26" s="5">
+        <v>16</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M26" s="5">
+        <v>1</v>
+      </c>
+      <c r="N26" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O26" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="16">
+        <v>46300</v>
+      </c>
+      <c r="I27" s="12">
+        <v>2</v>
+      </c>
+      <c r="J27" s="7">
+        <v>15</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M27" s="7">
+        <v>1</v>
+      </c>
+      <c r="N27" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O27" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="14">
+        <v>46300</v>
+      </c>
+      <c r="I28" s="10">
+        <v>2</v>
+      </c>
+      <c r="J28" s="5">
+        <v>16</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M28" s="5">
+        <v>1</v>
+      </c>
+      <c r="N28" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O28" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="16">
+        <v>46300</v>
+      </c>
+      <c r="I29" s="12">
+        <v>2</v>
+      </c>
+      <c r="J29" s="7">
+        <v>15</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M29" s="7">
+        <v>1</v>
+      </c>
+      <c r="N29" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O29" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="14">
+        <v>46300</v>
+      </c>
+      <c r="I30" s="10">
+        <v>2</v>
+      </c>
+      <c r="J30" s="5">
+        <v>16</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M30" s="5">
+        <v>1</v>
+      </c>
+      <c r="N30" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O30" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="16">
+        <v>46301</v>
+      </c>
+      <c r="I31" s="12">
+        <v>3</v>
+      </c>
+      <c r="J31" s="7">
+        <v>14</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M31" s="7">
+        <v>1</v>
+      </c>
+      <c r="N31" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O31" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="14">
-        <v>46296</v>
-      </c>
-      <c r="G8" s="10">
+      <c r="D32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="14">
+        <v>46301</v>
+      </c>
+      <c r="I32" s="10">
         <v>3</v>
       </c>
-      <c r="H8" s="5">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-      <c r="L8" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M8" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="J32" s="5">
+        <v>15</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M32" s="5">
+        <v>1</v>
+      </c>
+      <c r="N32" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O32" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="16">
+        <v>46301</v>
+      </c>
+      <c r="I33" s="12">
+        <v>3</v>
+      </c>
+      <c r="J33" s="7">
+        <v>16</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M33" s="7">
+        <v>1</v>
+      </c>
+      <c r="N33" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O33" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="14">
+        <v>46301</v>
+      </c>
+      <c r="I34" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="J34" s="5">
+        <v>14</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M34" s="5">
+        <v>1</v>
+      </c>
+      <c r="N34" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O34" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D35" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="16">
+        <v>46301</v>
+      </c>
+      <c r="I35" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="J35" s="7">
+        <v>15</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="16">
-        <v>46296</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="M35" s="7">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O35" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="14">
+        <v>46301</v>
+      </c>
+      <c r="I36" s="10">
+        <v>2</v>
+      </c>
+      <c r="J36" s="5">
+        <v>14</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M36" s="5">
+        <v>1</v>
+      </c>
+      <c r="N36" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O36" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="16">
+        <v>46301</v>
+      </c>
+      <c r="I37" s="12">
+        <v>2</v>
+      </c>
+      <c r="J37" s="7">
+        <v>15</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M37" s="7">
+        <v>1</v>
+      </c>
+      <c r="N37" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O37" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="14">
+        <v>46302</v>
+      </c>
+      <c r="I38" s="10">
+        <v>3</v>
+      </c>
+      <c r="J38" s="5">
+        <v>13</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M38" s="5">
+        <v>1</v>
+      </c>
+      <c r="N38" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O38" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="16">
+        <v>46302</v>
+      </c>
+      <c r="I39" s="12">
+        <v>3</v>
+      </c>
+      <c r="J39" s="7">
+        <v>14</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M39" s="7">
+        <v>1</v>
+      </c>
+      <c r="N39" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O39" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="14">
+        <v>46302</v>
+      </c>
+      <c r="I40" s="10">
+        <v>3</v>
+      </c>
+      <c r="J40" s="5">
+        <v>15</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M40" s="5">
+        <v>1</v>
+      </c>
+      <c r="N40" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O40" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="16">
+        <v>46302</v>
+      </c>
+      <c r="I41" s="12">
         <v>2.5</v>
       </c>
-      <c r="H9" s="7">
-        <v>19</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="7">
-        <v>1</v>
-      </c>
-      <c r="L9" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M9" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="J41" s="7">
+        <v>13</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="14">
-        <v>46296</v>
-      </c>
-      <c r="G10" s="10">
+      <c r="M41" s="7">
+        <v>1</v>
+      </c>
+      <c r="N41" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O41" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="14">
+        <v>46302</v>
+      </c>
+      <c r="I42" s="10">
         <v>2.5</v>
       </c>
-      <c r="H10" s="5">
-        <v>20</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="5">
-        <v>1</v>
-      </c>
-      <c r="L10" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M10" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="16">
-        <v>46296</v>
-      </c>
-      <c r="G11" s="12">
-        <v>2</v>
-      </c>
-      <c r="H11" s="7">
-        <v>19</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="7">
-        <v>1</v>
-      </c>
-      <c r="L11" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M11" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="J42" s="5">
+        <v>14</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M42" s="5">
+        <v>1</v>
+      </c>
+      <c r="N42" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O42" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="16">
+        <v>46302</v>
+      </c>
+      <c r="I43" s="12">
+        <v>2</v>
+      </c>
+      <c r="J43" s="7">
+        <v>13</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M43" s="7">
+        <v>1</v>
+      </c>
+      <c r="N43" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O43" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="14">
+        <v>46302</v>
+      </c>
+      <c r="I44" s="10">
+        <v>2</v>
+      </c>
+      <c r="J44" s="5">
+        <v>14</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M44" s="5">
+        <v>1</v>
+      </c>
+      <c r="N44" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O44" s="15">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C45" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="14">
-        <v>46296</v>
-      </c>
-      <c r="G12" s="10">
-        <v>2</v>
-      </c>
-      <c r="H12" s="5">
-        <v>20</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K12" s="5">
-        <v>1</v>
-      </c>
-      <c r="L12" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M12" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="D45" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="16">
+        <v>46302</v>
+      </c>
+      <c r="I45" s="12">
+        <v>2</v>
+      </c>
+      <c r="J45" s="7">
+        <v>13</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M45" s="7">
+        <v>1</v>
+      </c>
+      <c r="N45" s="17">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O45" s="17">
+        <v>46303.70653649306</v>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" s="16">
-        <v>46297</v>
-      </c>
-      <c r="G13" s="12">
-        <v>3</v>
-      </c>
-      <c r="H13" s="7">
-        <v>18</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K13" s="7">
-        <v>1</v>
-      </c>
-      <c r="L13" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M13" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="14">
-        <v>46297</v>
-      </c>
-      <c r="G14" s="10">
-        <v>3</v>
-      </c>
-      <c r="H14" s="5">
-        <v>19</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K14" s="5">
-        <v>1</v>
-      </c>
-      <c r="L14" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M14" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="16">
-        <v>46297</v>
-      </c>
-      <c r="G15" s="12">
-        <v>3</v>
-      </c>
-      <c r="H15" s="7">
-        <v>20</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="7">
-        <v>1</v>
-      </c>
-      <c r="L15" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M15" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="14">
-        <v>46297</v>
-      </c>
-      <c r="G16" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="H16" s="5">
-        <v>18</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="5">
-        <v>1</v>
-      </c>
-      <c r="L16" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M16" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" s="16">
-        <v>46297</v>
-      </c>
-      <c r="G17" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="H17" s="7">
-        <v>19</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K17" s="7">
-        <v>1</v>
-      </c>
-      <c r="L17" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M17" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="14">
-        <v>46297</v>
-      </c>
-      <c r="G18" s="10">
-        <v>2</v>
-      </c>
-      <c r="H18" s="5">
-        <v>18</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K18" s="5">
-        <v>1</v>
-      </c>
-      <c r="L18" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M18" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="16">
-        <v>46297</v>
-      </c>
-      <c r="G19" s="12">
-        <v>2</v>
-      </c>
-      <c r="H19" s="7">
-        <v>19</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K19" s="7">
-        <v>1</v>
-      </c>
-      <c r="L19" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M19" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" s="14">
-        <v>46297</v>
-      </c>
-      <c r="G20" s="10">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5">
-        <v>18</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K20" s="5">
-        <v>1</v>
-      </c>
-      <c r="L20" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M20" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="16">
-        <v>46297</v>
-      </c>
-      <c r="G21" s="12">
-        <v>2</v>
-      </c>
-      <c r="H21" s="7">
-        <v>19</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K21" s="7">
-        <v>1</v>
-      </c>
-      <c r="L21" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M21" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" s="14">
-        <v>46300</v>
-      </c>
-      <c r="G22" s="10">
-        <v>3</v>
-      </c>
-      <c r="H22" s="5">
-        <v>15</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K22" s="5">
-        <v>1</v>
-      </c>
-      <c r="L22" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M22" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="D46" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F23" s="16">
-        <v>46300</v>
-      </c>
-      <c r="G23" s="12">
-        <v>3</v>
-      </c>
-      <c r="H23" s="7">
-        <v>16</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K23" s="7">
-        <v>1</v>
-      </c>
-      <c r="L23" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M23" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="14">
-        <v>46300</v>
-      </c>
-      <c r="G24" s="10">
-        <v>3</v>
-      </c>
-      <c r="H24" s="5">
-        <v>17</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K24" s="5">
-        <v>1</v>
-      </c>
-      <c r="L24" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M24" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" s="16">
-        <v>46300</v>
-      </c>
-      <c r="G25" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="H25" s="7">
-        <v>15</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K25" s="7">
-        <v>1</v>
-      </c>
-      <c r="L25" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M25" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="14">
-        <v>46300</v>
-      </c>
-      <c r="G26" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="H26" s="5">
-        <v>16</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K26" s="5">
-        <v>1</v>
-      </c>
-      <c r="L26" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M26" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="16">
-        <v>46300</v>
-      </c>
-      <c r="G27" s="12">
-        <v>2</v>
-      </c>
-      <c r="H27" s="7">
-        <v>15</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K27" s="7">
-        <v>1</v>
-      </c>
-      <c r="L27" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M27" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="14">
-        <v>46300</v>
-      </c>
-      <c r="G28" s="10">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5">
-        <v>16</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K28" s="5">
-        <v>1</v>
-      </c>
-      <c r="L28" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M28" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" s="16">
-        <v>46300</v>
-      </c>
-      <c r="G29" s="12">
-        <v>2</v>
-      </c>
-      <c r="H29" s="7">
-        <v>15</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K29" s="7">
-        <v>1</v>
-      </c>
-      <c r="L29" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M29" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F30" s="14">
-        <v>46300</v>
-      </c>
-      <c r="G30" s="10">
-        <v>2</v>
-      </c>
-      <c r="H30" s="5">
-        <v>16</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K30" s="5">
-        <v>1</v>
-      </c>
-      <c r="L30" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M30" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="16">
-        <v>46301</v>
-      </c>
-      <c r="G31" s="12">
-        <v>3</v>
-      </c>
-      <c r="H31" s="7">
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="14">
+        <v>46302</v>
+      </c>
+      <c r="I46" s="10">
+        <v>2</v>
+      </c>
+      <c r="J46" s="5">
         <v>14</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K31" s="7">
-        <v>1</v>
-      </c>
-      <c r="L31" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M31" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="14">
-        <v>46301</v>
-      </c>
-      <c r="G32" s="10">
-        <v>3</v>
-      </c>
-      <c r="H32" s="5">
-        <v>15</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K32" s="5">
-        <v>1</v>
-      </c>
-      <c r="L32" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M32" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F33" s="16">
-        <v>46301</v>
-      </c>
-      <c r="G33" s="12">
-        <v>3</v>
-      </c>
-      <c r="H33" s="7">
-        <v>16</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K33" s="7">
-        <v>1</v>
-      </c>
-      <c r="L33" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M33" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="14">
-        <v>46301</v>
-      </c>
-      <c r="G34" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="H34" s="5">
-        <v>14</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K34" s="5">
-        <v>1</v>
-      </c>
-      <c r="L34" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M34" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="16">
-        <v>46301</v>
-      </c>
-      <c r="G35" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="H35" s="7">
-        <v>15</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K35" s="7">
-        <v>1</v>
-      </c>
-      <c r="L35" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M35" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="14">
-        <v>46301</v>
-      </c>
-      <c r="G36" s="10">
-        <v>2</v>
-      </c>
-      <c r="H36" s="5">
-        <v>14</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K36" s="5">
-        <v>1</v>
-      </c>
-      <c r="L36" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M36" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F37" s="16">
-        <v>46301</v>
-      </c>
-      <c r="G37" s="12">
-        <v>2</v>
-      </c>
-      <c r="H37" s="7">
-        <v>15</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K37" s="7">
-        <v>1</v>
-      </c>
-      <c r="L37" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M37" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="14">
-        <v>46302</v>
-      </c>
-      <c r="G38" s="10">
-        <v>3</v>
-      </c>
-      <c r="H38" s="5">
-        <v>13</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K38" s="5">
-        <v>1</v>
-      </c>
-      <c r="L38" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M38" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F39" s="16">
-        <v>46302</v>
-      </c>
-      <c r="G39" s="12">
-        <v>3</v>
-      </c>
-      <c r="H39" s="7">
-        <v>14</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K39" s="7">
-        <v>1</v>
-      </c>
-      <c r="L39" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M39" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F40" s="14">
-        <v>46302</v>
-      </c>
-      <c r="G40" s="10">
-        <v>3</v>
-      </c>
-      <c r="H40" s="5">
-        <v>15</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K40" s="5">
-        <v>1</v>
-      </c>
-      <c r="L40" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M40" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F41" s="16">
-        <v>46302</v>
-      </c>
-      <c r="G41" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="H41" s="7">
-        <v>13</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K41" s="7">
-        <v>1</v>
-      </c>
-      <c r="L41" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M41" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F42" s="14">
-        <v>46302</v>
-      </c>
-      <c r="G42" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="H42" s="5">
-        <v>14</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K42" s="5">
-        <v>1</v>
-      </c>
-      <c r="L42" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M42" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F43" s="16">
-        <v>46302</v>
-      </c>
-      <c r="G43" s="12">
-        <v>2</v>
-      </c>
-      <c r="H43" s="7">
-        <v>13</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K43" s="7">
-        <v>1</v>
-      </c>
-      <c r="L43" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M43" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F44" s="14">
-        <v>46302</v>
-      </c>
-      <c r="G44" s="10">
-        <v>2</v>
-      </c>
-      <c r="H44" s="5">
-        <v>14</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K44" s="5">
-        <v>1</v>
-      </c>
-      <c r="L44" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M44" s="15">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="16">
-        <v>46302</v>
-      </c>
-      <c r="G45" s="12">
-        <v>2</v>
-      </c>
-      <c r="H45" s="7">
-        <v>13</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K45" s="7">
-        <v>1</v>
-      </c>
-      <c r="L45" s="17">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M45" s="17">
-        <v>46303.35549128472</v>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F46" s="14">
-        <v>46302</v>
-      </c>
-      <c r="G46" s="10">
-        <v>2</v>
-      </c>
-      <c r="H46" s="5">
-        <v>14</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K46" s="5">
-        <v>1</v>
-      </c>
-      <c r="L46" s="15">
-        <v>46303.35549128472</v>
-      </c>
-      <c r="M46" s="15">
-        <v>46303.35549128472</v>
+      <c r="K46" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M46" s="5">
+        <v>1</v>
+      </c>
+      <c r="N46" s="15">
+        <v>46303.70653649306</v>
+      </c>
+      <c r="O46" s="15">
+        <v>46303.70653649306</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M46"/>
+  <autoFilter ref="A5:O46"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4265,7 +4559,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4361,72 +4655,72 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C6" s="14">
         <v>46296</v>
@@ -4438,16 +4732,16 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J6" s="5">
         <v>3</v>
@@ -4462,33 +4756,33 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R6" s="5">
         <v>1</v>
       </c>
       <c r="S6" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T6" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C7" s="16">
         <v>46296</v>
@@ -4500,16 +4794,16 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J7" s="7">
         <v>2</v>
@@ -4524,33 +4818,33 @@
         <v>2.5</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R7" s="7">
         <v>1</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T7" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C8" s="14">
         <v>46296</v>
@@ -4562,16 +4856,16 @@
         <v>0.625</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J8" s="5">
         <v>2</v>
@@ -4586,33 +4880,33 @@
         <v>2</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R8" s="5">
         <v>1</v>
       </c>
       <c r="S8" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T8" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C9" s="16">
         <v>46297</v>
@@ -4624,16 +4918,16 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
@@ -4648,33 +4942,33 @@
         <v>3</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R9" s="7">
         <v>1</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T9" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C10" s="14">
         <v>46297</v>
@@ -4686,16 +4980,16 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J10" s="5">
         <v>2</v>
@@ -4710,33 +5004,33 @@
         <v>2.5</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R10" s="5">
         <v>1</v>
       </c>
       <c r="S10" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T10" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C11" s="16">
         <v>46297</v>
@@ -4748,16 +5042,16 @@
         <v>0.625</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J11" s="7">
         <v>2</v>
@@ -4772,33 +5066,33 @@
         <v>2</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R11" s="7">
         <v>1</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T11" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C12" s="14">
         <v>46297</v>
@@ -4810,16 +5104,16 @@
         <v>0.5</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J12" s="5">
         <v>2</v>
@@ -4834,33 +5128,33 @@
         <v>2</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R12" s="5">
         <v>1</v>
       </c>
       <c r="S12" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T12" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="16">
         <v>46300</v>
@@ -4872,16 +5166,16 @@
         <v>0.5</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J13" s="7">
         <v>3</v>
@@ -4896,33 +5190,33 @@
         <v>3</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R13" s="7">
         <v>1</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T13" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" s="14">
         <v>46300</v>
@@ -4934,16 +5228,16 @@
         <v>0.5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J14" s="5">
         <v>2</v>
@@ -4958,33 +5252,33 @@
         <v>2.5</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R14" s="5">
         <v>1</v>
       </c>
       <c r="S14" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T14" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C15" s="16">
         <v>46300</v>
@@ -4996,16 +5290,16 @@
         <v>0.625</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J15" s="7">
         <v>2</v>
@@ -5020,33 +5314,33 @@
         <v>2</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R15" s="7">
         <v>1</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T15" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C16" s="14">
         <v>46300</v>
@@ -5058,16 +5352,16 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J16" s="5">
         <v>2</v>
@@ -5082,33 +5376,33 @@
         <v>2</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R16" s="5">
         <v>1</v>
       </c>
       <c r="S16" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T16" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C17" s="16">
         <v>46301</v>
@@ -5120,16 +5414,16 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J17" s="7">
         <v>3</v>
@@ -5144,33 +5438,33 @@
         <v>3</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R17" s="7">
         <v>1</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T17" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C18" s="14">
         <v>46301</v>
@@ -5182,16 +5476,16 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J18" s="5">
         <v>2</v>
@@ -5206,33 +5500,33 @@
         <v>2.5</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R18" s="5">
         <v>1</v>
       </c>
       <c r="S18" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T18" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C19" s="16">
         <v>46301</v>
@@ -5244,16 +5538,16 @@
         <v>0.625</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J19" s="7">
         <v>2</v>
@@ -5268,33 +5562,33 @@
         <v>2</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R19" s="7">
         <v>1</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T19" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C20" s="14">
         <v>46302</v>
@@ -5306,16 +5600,16 @@
         <v>0.5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J20" s="5">
         <v>3</v>
@@ -5330,33 +5624,33 @@
         <v>3</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R20" s="5">
         <v>1</v>
       </c>
       <c r="S20" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T20" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C21" s="16">
         <v>46302</v>
@@ -5368,16 +5662,16 @@
         <v>0.5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J21" s="7">
         <v>2</v>
@@ -5392,33 +5686,33 @@
         <v>2.5</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R21" s="7">
         <v>1</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T21" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C22" s="14">
         <v>46302</v>
@@ -5430,16 +5724,16 @@
         <v>0.625</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J22" s="5">
         <v>2</v>
@@ -5454,33 +5748,33 @@
         <v>2</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R22" s="5">
         <v>1</v>
       </c>
       <c r="S22" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T22" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C23" s="16">
         <v>46302</v>
@@ -5492,16 +5786,16 @@
         <v>0.5</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -5516,33 +5810,33 @@
         <v>2</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R23" s="7">
         <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T23" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C24" s="14">
         <v>46303</v>
@@ -5554,16 +5848,16 @@
         <v>0.5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J24" s="5">
         <v>3</v>
@@ -5578,33 +5872,33 @@
         <v>3</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R24" s="5">
         <v>1</v>
       </c>
       <c r="S24" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T24" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C25" s="16">
         <v>46303</v>
@@ -5616,16 +5910,16 @@
         <v>0.5</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
@@ -5640,33 +5934,33 @@
         <v>2.5</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R25" s="7">
         <v>1</v>
       </c>
       <c r="S25" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T25" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C26" s="14">
         <v>46303</v>
@@ -5678,57 +5972,57 @@
         <v>0.625</v>
       </c>
       <c r="F26" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J26" s="5">
+        <v>2</v>
+      </c>
+      <c r="K26" s="5">
+        <v>1</v>
+      </c>
+      <c r="L26" s="5">
+        <v>1</v>
+      </c>
+      <c r="M26" s="10">
+        <v>2</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="P26" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="Q26" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="J26" s="5">
-        <v>2</v>
-      </c>
-      <c r="K26" s="5">
-        <v>1</v>
-      </c>
-      <c r="L26" s="5">
-        <v>1</v>
-      </c>
-      <c r="M26" s="10">
-        <v>2</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="R26" s="5">
         <v>1</v>
       </c>
       <c r="S26" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T26" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C27" s="16">
         <v>46304</v>
@@ -5740,16 +6034,16 @@
         <v>0.5</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J27" s="7">
         <v>3</v>
@@ -5764,33 +6058,33 @@
         <v>3</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R27" s="7">
         <v>1</v>
       </c>
       <c r="S27" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T27" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C28" s="14">
         <v>46304</v>
@@ -5802,16 +6096,16 @@
         <v>0.5</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J28" s="5">
         <v>2</v>
@@ -5826,33 +6120,33 @@
         <v>2.5</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R28" s="5">
         <v>1</v>
       </c>
       <c r="S28" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T28" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C29" s="16">
         <v>46304</v>
@@ -5864,16 +6158,16 @@
         <v>0.625</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J29" s="7">
         <v>2</v>
@@ -5888,33 +6182,33 @@
         <v>2</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R29" s="7">
         <v>1</v>
       </c>
       <c r="S29" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T29" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C30" s="14">
         <v>46304</v>
@@ -5926,16 +6220,16 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J30" s="5">
         <v>2</v>
@@ -5950,33 +6244,33 @@
         <v>2</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R30" s="5">
         <v>1</v>
       </c>
       <c r="S30" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T30" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C31" s="16">
         <v>46307</v>
@@ -5988,16 +6282,16 @@
         <v>0.5</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J31" s="7">
         <v>3</v>
@@ -6012,33 +6306,33 @@
         <v>3</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R31" s="7">
         <v>1</v>
       </c>
       <c r="S31" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T31" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C32" s="14">
         <v>46307</v>
@@ -6050,16 +6344,16 @@
         <v>0.5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J32" s="5">
         <v>2</v>
@@ -6074,33 +6368,33 @@
         <v>2.5</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R32" s="5">
         <v>1</v>
       </c>
       <c r="S32" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T32" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C33" s="16">
         <v>46307</v>
@@ -6112,16 +6406,16 @@
         <v>0.625</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J33" s="7">
         <v>2</v>
@@ -6136,33 +6430,33 @@
         <v>2</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R33" s="7">
         <v>1</v>
       </c>
       <c r="S33" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T33" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C34" s="14">
         <v>46307</v>
@@ -6174,16 +6468,16 @@
         <v>0.5</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J34" s="5">
         <v>2</v>
@@ -6198,33 +6492,33 @@
         <v>2</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R34" s="5">
         <v>1</v>
       </c>
       <c r="S34" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T34" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C35" s="16">
         <v>46308</v>
@@ -6236,16 +6530,16 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J35" s="7">
         <v>3</v>
@@ -6260,33 +6554,33 @@
         <v>3</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R35" s="7">
         <v>1</v>
       </c>
       <c r="S35" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T35" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C36" s="14">
         <v>46308</v>
@@ -6298,16 +6592,16 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J36" s="5">
         <v>2</v>
@@ -6322,33 +6616,33 @@
         <v>2.5</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R36" s="5">
         <v>1</v>
       </c>
       <c r="S36" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T36" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C37" s="16">
         <v>46308</v>
@@ -6360,16 +6654,16 @@
         <v>0.625</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J37" s="7">
         <v>2</v>
@@ -6384,33 +6678,33 @@
         <v>2</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R37" s="7">
         <v>1</v>
       </c>
       <c r="S37" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T37" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C38" s="14">
         <v>46309</v>
@@ -6422,16 +6716,16 @@
         <v>0.5</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J38" s="5">
         <v>3</v>
@@ -6446,33 +6740,33 @@
         <v>3</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R38" s="5">
         <v>1</v>
       </c>
       <c r="S38" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T38" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C39" s="16">
         <v>46309</v>
@@ -6484,16 +6778,16 @@
         <v>0.5</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J39" s="7">
         <v>2</v>
@@ -6508,33 +6802,33 @@
         <v>2.5</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R39" s="7">
         <v>1</v>
       </c>
       <c r="S39" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T39" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C40" s="14">
         <v>46309</v>
@@ -6546,16 +6840,16 @@
         <v>0.625</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J40" s="5">
         <v>2</v>
@@ -6570,33 +6864,33 @@
         <v>2</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R40" s="5">
         <v>1</v>
       </c>
       <c r="S40" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T40" s="15">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C41" s="16">
         <v>46309</v>
@@ -6608,16 +6902,16 @@
         <v>0.5</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J41" s="7">
         <v>2</v>
@@ -6632,25 +6926,25 @@
         <v>2</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R41" s="7">
         <v>1</v>
       </c>
       <c r="S41" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
       <c r="T41" s="17">
-        <v>46303.35549128472</v>
+        <v>46303.70653649306</v>
       </c>
     </row>
   </sheetData>
@@ -6696,7 +6990,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6768,54 +7062,54 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C6" s="14">
         <v>46296</v>
@@ -6827,37 +7121,37 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L6" s="10">
         <v>3</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N6" s="4"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C7" s="16">
         <v>46296</v>
@@ -6869,37 +7163,37 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L7" s="12">
         <v>3</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N7" s="6"/>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C8" s="14">
         <v>46296</v>
@@ -6911,37 +7205,37 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L8" s="10">
         <v>3</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N8" s="4"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C9" s="16">
         <v>46296</v>
@@ -6953,37 +7247,37 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="L9" s="12">
         <v>2.5</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N9" s="6"/>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C10" s="14">
         <v>46296</v>
@@ -6995,37 +7289,37 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="L10" s="10">
         <v>2.5</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N10" s="4"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C11" s="16">
         <v>46296</v>
@@ -7037,37 +7331,37 @@
         <v>0.625</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L11" s="12">
         <v>2</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N11" s="6"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C12" s="14">
         <v>46296</v>
@@ -7079,37 +7373,37 @@
         <v>0.625</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L12" s="10">
         <v>2</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N12" s="4"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="16">
         <v>46297</v>
@@ -7121,37 +7415,37 @@
         <v>0.5</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L13" s="12">
         <v>3</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N13" s="6"/>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C14" s="14">
         <v>46297</v>
@@ -7163,37 +7457,37 @@
         <v>0.5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L14" s="10">
         <v>3</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N14" s="4"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C15" s="16">
         <v>46297</v>
@@ -7205,37 +7499,37 @@
         <v>0.5</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L15" s="12">
         <v>3</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N15" s="6"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="14">
         <v>46297</v>
@@ -7247,37 +7541,37 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="L16" s="10">
         <v>2.5</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N16" s="4"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C17" s="16">
         <v>46297</v>
@@ -7289,37 +7583,37 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="L17" s="12">
         <v>2.5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N17" s="6"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C18" s="14">
         <v>46297</v>
@@ -7331,37 +7625,37 @@
         <v>0.625</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L18" s="10">
         <v>2</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N18" s="4"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C19" s="16">
         <v>46297</v>
@@ -7373,37 +7667,37 @@
         <v>0.625</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L19" s="12">
         <v>2</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N19" s="6"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C20" s="14">
         <v>46297</v>
@@ -7415,37 +7709,37 @@
         <v>0.5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L20" s="10">
         <v>2</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N20" s="4"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C21" s="16">
         <v>46297</v>
@@ -7457,37 +7751,37 @@
         <v>0.5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L21" s="12">
         <v>2</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N21" s="6"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C22" s="14">
         <v>46300</v>
@@ -7499,37 +7793,37 @@
         <v>0.5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L22" s="10">
         <v>3</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N22" s="4"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C23" s="16">
         <v>46300</v>
@@ -7541,37 +7835,37 @@
         <v>0.5</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L23" s="12">
         <v>3</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N23" s="6"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C24" s="14">
         <v>46300</v>
@@ -7583,37 +7877,37 @@
         <v>0.5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L24" s="10">
         <v>3</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N24" s="4"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C25" s="16">
         <v>46300</v>
@@ -7625,37 +7919,37 @@
         <v>0.5</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H25" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K25" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="L25" s="12">
         <v>2.5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N25" s="6"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C26" s="14">
         <v>46300</v>
@@ -7667,37 +7961,37 @@
         <v>0.5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H26" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="L26" s="10">
         <v>2.5</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N26" s="4"/>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C27" s="16">
         <v>46300</v>
@@ -7709,37 +8003,37 @@
         <v>0.625</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L27" s="12">
         <v>2</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N27" s="6"/>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C28" s="14">
         <v>46300</v>
@@ -7751,37 +8045,37 @@
         <v>0.625</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L28" s="10">
         <v>2</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N28" s="4"/>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C29" s="16">
         <v>46300</v>
@@ -7793,37 +8087,37 @@
         <v>0.5</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L29" s="12">
         <v>2</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N29" s="6"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C30" s="14">
         <v>46300</v>
@@ -7835,37 +8129,37 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L30" s="10">
         <v>2</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N30" s="4"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C31" s="16">
         <v>46301</v>
@@ -7877,37 +8171,37 @@
         <v>0.5</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L31" s="12">
         <v>3</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N31" s="6"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C32" s="14">
         <v>46301</v>
@@ -7919,37 +8213,37 @@
         <v>0.5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L32" s="10">
         <v>3</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N32" s="4"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C33" s="16">
         <v>46301</v>
@@ -7961,37 +8255,37 @@
         <v>0.5</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L33" s="12">
         <v>3</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N33" s="6"/>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C34" s="14">
         <v>46301</v>
@@ -8003,37 +8297,37 @@
         <v>0.5</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H34" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K34" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="L34" s="10">
         <v>2.5</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N34" s="4"/>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C35" s="16">
         <v>46301</v>
@@ -8045,37 +8339,37 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H35" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K35" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="L35" s="12">
         <v>2.5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N35" s="6"/>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C36" s="14">
         <v>46301</v>
@@ -8087,37 +8381,37 @@
         <v>0.625</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L36" s="10">
         <v>2</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N36" s="4"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C37" s="16">
         <v>46301</v>
@@ -8129,37 +8423,37 @@
         <v>0.625</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L37" s="12">
         <v>2</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N37" s="6"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C38" s="14">
         <v>46302</v>
@@ -8171,37 +8465,37 @@
         <v>0.5</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L38" s="10">
         <v>3</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N38" s="4"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C39" s="16">
         <v>46302</v>
@@ -8213,37 +8507,37 @@
         <v>0.5</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L39" s="12">
         <v>3</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N39" s="6"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C40" s="14">
         <v>46302</v>
@@ -8255,37 +8549,37 @@
         <v>0.5</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L40" s="10">
         <v>3</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N40" s="4"/>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C41" s="16">
         <v>46302</v>
@@ -8297,37 +8591,37 @@
         <v>0.5</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H41" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K41" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="L41" s="12">
         <v>2.5</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N41" s="6"/>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C42" s="14">
         <v>46302</v>
@@ -8339,37 +8633,37 @@
         <v>0.5</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H42" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K42" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="L42" s="10">
         <v>2.5</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N42" s="4"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C43" s="16">
         <v>46302</v>
@@ -8381,37 +8675,37 @@
         <v>0.625</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L43" s="12">
         <v>2</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N43" s="6"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C44" s="14">
         <v>46302</v>
@@ -8423,37 +8717,37 @@
         <v>0.625</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L44" s="10">
         <v>2</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N44" s="4"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C45" s="16">
         <v>46302</v>
@@ -8465,37 +8759,37 @@
         <v>0.5</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L45" s="12">
         <v>2</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N45" s="6"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C46" s="14">
         <v>46302</v>
@@ -8507,37 +8801,37 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L46" s="10">
         <v>2</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N46" s="4"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C47" s="16">
         <v>46303</v>
@@ -8549,37 +8843,37 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L47" s="12">
         <v>3</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N47" s="6"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C48" s="14">
         <v>46303</v>
@@ -8591,37 +8885,37 @@
         <v>0.5</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L48" s="10">
         <v>3</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N48" s="4"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C49" s="16">
         <v>46303</v>
@@ -8633,37 +8927,37 @@
         <v>0.5</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L49" s="12">
         <v>2.5</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N49" s="6"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C50" s="14">
         <v>46303</v>
@@ -8675,28 +8969,28 @@
         <v>0.625</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L50" s="10">
         <v>2</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N50" s="4"/>
     </row>

--- a/artifacts/exports/shuori-demo-monthly-report.xlsx
+++ b/artifacts/exports/shuori-demo-monthly-report.xlsx
@@ -47,7 +47,7 @@
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 17:07:00 JST · Asia/Tokyo · demo · version 1.3.0</t>
+    <t>Generated 2026-10-08 17:31:48 JST · Asia/Tokyo · demo · version 1.3.0</t>
   </si>
   <si>
     <t>monthly-report | All records in the stated scope | Month: 2026-10 | View label: 2026-10 | activity and participation</t>
@@ -629,7 +629,7 @@
     <t>library</t>
   </si>
   <si>
-    <t>Nikoniko Bunko Plus</t>
+    <t>Library</t>
   </si>
   <si>
     <t>6F</t>
@@ -2786,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O6" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2829,10 +2829,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2872,10 +2872,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O8" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2915,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2958,10 +2958,10 @@
         <v>1</v>
       </c>
       <c r="N10" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O10" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3001,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="N11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3044,10 +3044,10 @@
         <v>1</v>
       </c>
       <c r="N12" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O12" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>1</v>
       </c>
       <c r="N13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3130,10 +3130,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O14" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3173,10 +3173,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O16" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3259,10 +3259,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3302,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="N18" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O18" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3345,10 +3345,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3388,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="N20" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O20" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3431,10 +3431,10 @@
         <v>1</v>
       </c>
       <c r="N21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3474,10 +3474,10 @@
         <v>1</v>
       </c>
       <c r="N22" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O22" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3517,10 +3517,10 @@
         <v>1</v>
       </c>
       <c r="N23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3560,10 +3560,10 @@
         <v>1</v>
       </c>
       <c r="N24" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O24" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3603,10 +3603,10 @@
         <v>1</v>
       </c>
       <c r="N25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3646,10 +3646,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O26" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3689,10 +3689,10 @@
         <v>1</v>
       </c>
       <c r="N27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3732,10 +3732,10 @@
         <v>1</v>
       </c>
       <c r="N28" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O28" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3775,10 +3775,10 @@
         <v>1</v>
       </c>
       <c r="N29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3818,10 +3818,10 @@
         <v>1</v>
       </c>
       <c r="N30" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O30" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3861,10 +3861,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3904,10 +3904,10 @@
         <v>1</v>
       </c>
       <c r="N32" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O32" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3947,10 +3947,10 @@
         <v>1</v>
       </c>
       <c r="N33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3990,10 +3990,10 @@
         <v>1</v>
       </c>
       <c r="N34" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O34" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4033,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="N35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4076,10 +4076,10 @@
         <v>1</v>
       </c>
       <c r="N36" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O36" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4119,10 +4119,10 @@
         <v>1</v>
       </c>
       <c r="N37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4162,10 +4162,10 @@
         <v>1</v>
       </c>
       <c r="N38" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O38" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4205,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="N39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4248,10 +4248,10 @@
         <v>1</v>
       </c>
       <c r="N40" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O40" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4291,10 +4291,10 @@
         <v>1</v>
       </c>
       <c r="N41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4334,10 +4334,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O42" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4377,10 +4377,10 @@
         <v>1</v>
       </c>
       <c r="N43" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O43" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4420,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="N44" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O44" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4463,10 +4463,10 @@
         <v>1</v>
       </c>
       <c r="N45" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O45" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4506,10 +4506,10 @@
         <v>1</v>
       </c>
       <c r="N46" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O46" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -4771,10 +4771,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T6" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4833,10 +4833,10 @@
         <v>1</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4895,10 +4895,10 @@
         <v>1</v>
       </c>
       <c r="S8" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T8" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5019,10 +5019,10 @@
         <v>1</v>
       </c>
       <c r="S10" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T10" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5081,10 +5081,10 @@
         <v>1</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5143,10 +5143,10 @@
         <v>1</v>
       </c>
       <c r="S12" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T12" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5205,10 +5205,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5267,10 +5267,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T14" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5329,10 +5329,10 @@
         <v>1</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5391,10 +5391,10 @@
         <v>1</v>
       </c>
       <c r="S16" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T16" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5453,10 +5453,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5515,10 +5515,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T18" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5577,10 +5577,10 @@
         <v>1</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5639,10 +5639,10 @@
         <v>1</v>
       </c>
       <c r="S20" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T20" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5701,10 +5701,10 @@
         <v>1</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5763,10 +5763,10 @@
         <v>1</v>
       </c>
       <c r="S22" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T22" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5825,10 +5825,10 @@
         <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5887,10 +5887,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T24" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="S25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6011,10 +6011,10 @@
         <v>1</v>
       </c>
       <c r="S26" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T26" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6073,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="S27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6135,10 +6135,10 @@
         <v>1</v>
       </c>
       <c r="S28" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T28" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6197,10 +6197,10 @@
         <v>1</v>
       </c>
       <c r="S29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6259,10 +6259,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T30" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6321,10 +6321,10 @@
         <v>1</v>
       </c>
       <c r="S31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6383,10 +6383,10 @@
         <v>1</v>
       </c>
       <c r="S32" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T32" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6445,10 +6445,10 @@
         <v>1</v>
       </c>
       <c r="S33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6507,10 +6507,10 @@
         <v>1</v>
       </c>
       <c r="S34" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T34" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6569,10 +6569,10 @@
         <v>1</v>
       </c>
       <c r="S35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6631,10 +6631,10 @@
         <v>1</v>
       </c>
       <c r="S36" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T36" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6693,10 +6693,10 @@
         <v>1</v>
       </c>
       <c r="S37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6755,10 +6755,10 @@
         <v>1</v>
       </c>
       <c r="S38" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T38" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6817,10 +6817,10 @@
         <v>1</v>
       </c>
       <c r="S39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6879,10 +6879,10 @@
         <v>1</v>
       </c>
       <c r="S40" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T40" s="15">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6941,10 +6941,10 @@
         <v>1</v>
       </c>
       <c r="S41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/exports/shuori-demo-monthly-report.xlsx
+++ b/artifacts/exports/shuori-demo-monthly-report.xlsx
@@ -47,7 +47,7 @@
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 17:31:48 JST · Asia/Tokyo · demo · version 1.3.0</t>
+    <t>Generated 2026-10-08 18:03:40 JST · Asia/Tokyo · demo · version 1.4.0</t>
   </si>
   <si>
     <t>monthly-report | All records in the stated scope | Month: 2026-10 | View label: 2026-10 | activity and participation</t>
@@ -2786,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O6" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2829,10 +2829,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2872,10 +2872,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O8" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2915,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2958,10 +2958,10 @@
         <v>1</v>
       </c>
       <c r="N10" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O10" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3001,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="N11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3044,10 +3044,10 @@
         <v>1</v>
       </c>
       <c r="N12" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O12" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>1</v>
       </c>
       <c r="N13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3130,10 +3130,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O14" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3173,10 +3173,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O16" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3259,10 +3259,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3302,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="N18" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O18" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3345,10 +3345,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3388,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="N20" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O20" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3431,10 +3431,10 @@
         <v>1</v>
       </c>
       <c r="N21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3474,10 +3474,10 @@
         <v>1</v>
       </c>
       <c r="N22" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O22" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3517,10 +3517,10 @@
         <v>1</v>
       </c>
       <c r="N23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3560,10 +3560,10 @@
         <v>1</v>
       </c>
       <c r="N24" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O24" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3603,10 +3603,10 @@
         <v>1</v>
       </c>
       <c r="N25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3646,10 +3646,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O26" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3689,10 +3689,10 @@
         <v>1</v>
       </c>
       <c r="N27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3732,10 +3732,10 @@
         <v>1</v>
       </c>
       <c r="N28" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O28" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3775,10 +3775,10 @@
         <v>1</v>
       </c>
       <c r="N29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3818,10 +3818,10 @@
         <v>1</v>
       </c>
       <c r="N30" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O30" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3861,10 +3861,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3904,10 +3904,10 @@
         <v>1</v>
       </c>
       <c r="N32" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O32" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3947,10 +3947,10 @@
         <v>1</v>
       </c>
       <c r="N33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -3990,10 +3990,10 @@
         <v>1</v>
       </c>
       <c r="N34" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O34" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4033,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="N35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4076,10 +4076,10 @@
         <v>1</v>
       </c>
       <c r="N36" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O36" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4119,10 +4119,10 @@
         <v>1</v>
       </c>
       <c r="N37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4162,10 +4162,10 @@
         <v>1</v>
       </c>
       <c r="N38" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O38" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4205,10 +4205,10 @@
         <v>1</v>
       </c>
       <c r="N39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4248,10 +4248,10 @@
         <v>1</v>
       </c>
       <c r="N40" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O40" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4291,10 +4291,10 @@
         <v>1</v>
       </c>
       <c r="N41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4334,10 +4334,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O42" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4377,10 +4377,10 @@
         <v>1</v>
       </c>
       <c r="N43" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O43" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4420,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="N44" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O44" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4463,10 +4463,10 @@
         <v>1</v>
       </c>
       <c r="N45" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O45" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4506,10 +4506,10 @@
         <v>1</v>
       </c>
       <c r="N46" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O46" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -4771,10 +4771,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T6" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4833,10 +4833,10 @@
         <v>1</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4895,10 +4895,10 @@
         <v>1</v>
       </c>
       <c r="S8" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T8" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -4957,10 +4957,10 @@
         <v>1</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5019,10 +5019,10 @@
         <v>1</v>
       </c>
       <c r="S10" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T10" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5081,10 +5081,10 @@
         <v>1</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5143,10 +5143,10 @@
         <v>1</v>
       </c>
       <c r="S12" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T12" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5205,10 +5205,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5267,10 +5267,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T14" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5329,10 +5329,10 @@
         <v>1</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5391,10 +5391,10 @@
         <v>1</v>
       </c>
       <c r="S16" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T16" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5453,10 +5453,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5515,10 +5515,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T18" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5577,10 +5577,10 @@
         <v>1</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5639,10 +5639,10 @@
         <v>1</v>
       </c>
       <c r="S20" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T20" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5701,10 +5701,10 @@
         <v>1</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5763,10 +5763,10 @@
         <v>1</v>
       </c>
       <c r="S22" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T22" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5825,10 +5825,10 @@
         <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5887,10 +5887,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T24" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="S25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6011,10 +6011,10 @@
         <v>1</v>
       </c>
       <c r="S26" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T26" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6073,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="S27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6135,10 +6135,10 @@
         <v>1</v>
       </c>
       <c r="S28" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T28" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6197,10 +6197,10 @@
         <v>1</v>
       </c>
       <c r="S29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6259,10 +6259,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T30" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6321,10 +6321,10 @@
         <v>1</v>
       </c>
       <c r="S31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6383,10 +6383,10 @@
         <v>1</v>
       </c>
       <c r="S32" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T32" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6445,10 +6445,10 @@
         <v>1</v>
       </c>
       <c r="S33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6507,10 +6507,10 @@
         <v>1</v>
       </c>
       <c r="S34" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T34" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6569,10 +6569,10 @@
         <v>1</v>
       </c>
       <c r="S35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6631,10 +6631,10 @@
         <v>1</v>
       </c>
       <c r="S36" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T36" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6693,10 +6693,10 @@
         <v>1</v>
       </c>
       <c r="S37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6755,10 +6755,10 @@
         <v>1</v>
       </c>
       <c r="S38" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T38" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6817,10 +6817,10 @@
         <v>1</v>
       </c>
       <c r="S39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6879,10 +6879,10 @@
         <v>1</v>
       </c>
       <c r="S40" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T40" s="15">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6941,10 +6941,10 @@
         <v>1</v>
       </c>
       <c r="S41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
